--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -43021,13 +43021,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O245" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R245" t="n">
-        <v>0.1143402255037307</v>
+        <v>0.1162781954275228</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -43530,12 +43530,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43569,81 +43569,100 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="O248" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="R248" t="n">
-        <v>0.07822246403586412</v>
+        <v>0.2616566519919337</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43670,17 +43689,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -43714,81 +43733,175 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="O249" t="n">
-        <v>71</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0.02034177074266263</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>Legionellainfektion</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN249" t="b">
+        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43820,12 +43933,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43850,7 +43963,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -43859,13 +43972,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="O250" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="R250" t="n">
-        <v>0.04329084560098561</v>
+        <v>0.07822246403586412</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -43898,42 +44011,42 @@
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43965,12 +44078,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -43995,7 +44108,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -44004,93 +44117,81 @@
         </is>
       </c>
       <c r="N251" t="n">
+        <v>71</v>
+      </c>
+      <c r="O251" t="n">
+        <v>71</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.02034177074266263</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="n">
         <v>0</v>
       </c>
-      <c r="O251" t="n">
-        <v>0</v>
-      </c>
-      <c r="P251" t="n">
-        <v>0</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO251" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP251" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ251" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT251" t="n">
-        <v>2</v>
-      </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44117,17 +44218,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44161,173 +44262,81 @@
         </is>
       </c>
       <c r="N252" t="n">
+        <v>53</v>
+      </c>
+      <c r="O252" t="n">
+        <v>53</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0.04329084560098561</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
+      <c r="AT252" t="n">
         <v>0</v>
       </c>
-      <c r="O252" t="n">
-        <v>0</v>
-      </c>
-      <c r="P252" t="n">
-        <v>0</v>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V252" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD252" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE252" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF252" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG252" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH252" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ252" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK252" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM252" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN252" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO252" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP252" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT252" t="n">
-        <v>2</v>
-      </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44359,12 +44368,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44389,7 +44398,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -44398,81 +44407,93 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>92</v>
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>0.02635835082147835</v>
+        <v>0</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44499,17 +44520,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44534,7 +44555,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -44543,81 +44564,173 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
-        <v>60</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.04900850445394597</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44649,12 +44762,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44679,7 +44792,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -44688,93 +44801,81 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="O255" t="n">
-        <v>1</v>
-      </c>
-      <c r="P255" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="R255" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.02635835082147835</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44801,17 +44902,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -44845,173 +44946,81 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="O256" t="n">
-        <v>1</v>
-      </c>
-      <c r="P256" t="n">
-        <v>1</v>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W256" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y256" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD256" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE256" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF256" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG256" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ256" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK256" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM256" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN256" t="b">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0.04900850445394597</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45043,12 +45052,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45073,7 +45082,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -45082,81 +45091,93 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="O257" t="n">
-        <v>134</v>
+        <v>1</v>
+      </c>
+      <c r="P257" t="n">
+        <v>1</v>
       </c>
       <c r="R257" t="n">
-        <v>0.03839151097910976</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45183,17 +45204,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45218,7 +45239,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45227,81 +45248,173 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="O258" t="n">
-        <v>45</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0.03675637834045948</v>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P258" t="n">
+        <v>1</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45333,12 +45446,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45363,7 +45476,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -45372,93 +45485,81 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="O259" t="n">
-        <v>2</v>
-      </c>
-      <c r="P259" t="n">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="R259" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.03839151097910976</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45485,17 +45586,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45529,173 +45630,81 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O260" t="n">
-        <v>2</v>
-      </c>
-      <c r="P260" t="n">
-        <v>2</v>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN260" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0.03675637834045948</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ260" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45727,12 +45736,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45757,7 +45766,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -45766,81 +45775,93 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="O261" t="n">
-        <v>83</v>
+        <v>2</v>
+      </c>
+      <c r="P261" t="n">
+        <v>2</v>
       </c>
       <c r="R261" t="n">
-        <v>0.0237798165019859</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45867,17 +45888,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -45902,7 +45923,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -45911,81 +45932,173 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="O262" t="n">
-        <v>41</v>
-      </c>
-      <c r="R262" t="n">
-        <v>0.03348914471019642</v>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P262" t="n">
+        <v>2</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN262" t="b">
+        <v>1</v>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46017,12 +46130,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46047,7 +46160,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -46056,93 +46169,81 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="O263" t="n">
-        <v>2</v>
-      </c>
-      <c r="P263" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="R263" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0237798165019859</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ263" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46169,17 +46270,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46213,173 +46314,81 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="O264" t="n">
-        <v>2</v>
-      </c>
-      <c r="P264" t="n">
-        <v>2</v>
-      </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W264" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA264" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG264" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK264" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN264" t="b">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0.03348914471019642</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46411,12 +46420,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46441,7 +46450,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -46450,81 +46459,93 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="O265" t="n">
-        <v>116</v>
+        <v>2</v>
+      </c>
+      <c r="P265" t="n">
+        <v>2</v>
       </c>
       <c r="R265" t="n">
-        <v>0.03323444234012487</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46551,17 +46572,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46586,90 +46607,182 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
-      </c>
-      <c r="R266" t="n">
-        <v>0</v>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P266" t="n">
+        <v>2</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN266" t="b">
+        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46701,12 +46814,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46731,109 +46844,90 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N267" t="n">
+        <v>116</v>
+      </c>
+      <c r="O267" t="n">
+        <v>116</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0.03323444234012487</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
+      <c r="AT267" t="n">
         <v>0</v>
       </c>
-      <c r="O267" t="n">
-        <v>0</v>
-      </c>
-      <c r="R267" t="n">
-        <v>0</v>
-      </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO267" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP267" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AT267" t="n">
-        <v>2</v>
-      </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46860,17 +46954,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -46909,170 +47003,76 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
+      <c r="AT268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV268" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN268" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO268" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP268" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AT268" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU268" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV268" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47104,12 +47104,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47143,81 +47143,100 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>0.009689849618960231</v>
+        <v>0</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47244,17 +47263,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47293,17 +47312,34 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="R270" t="n">
-        <v>0</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -47311,6 +47347,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47323,7 +47417,7 @@
       </c>
       <c r="AQ270" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR270" t="inlineStr">
@@ -47333,7 +47427,7 @@
       </c>
       <c r="AS270" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT270" t="n">
@@ -47341,47 +47435,47 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47408,217 +47502,526 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>8</v>
+      </c>
+      <c r="O271" t="n">
+        <v>8</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0.01550375939033637</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
+      <c r="AT271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA271" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC271" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F273" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
+      <c r="G273" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>D107</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
         <is>
           <t>军团菌病</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
+      <c r="K273" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
+      <c r="L273" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr">
+      <c r="M273" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N271" t="n">
+      <c r="N273" t="n">
         <v>0</v>
       </c>
-      <c r="O271" t="n">
+      <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="U273" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="V271" t="inlineStr">
+      <c r="V273" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="W271" t="inlineStr">
+      <c r="W273" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X271" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>Legionellose</t>
         </is>
       </c>
-      <c r="Y271" t="inlineStr">
+      <c r="Y273" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z271" t="inlineStr">
+      <c r="Z273" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA271" t="inlineStr">
+      <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB271" t="inlineStr">
+      <c r="AB273" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC271" t="inlineStr">
+      <c r="AC273" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD271" t="inlineStr">
+      <c r="AD273" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE271" t="inlineStr">
+      <c r="AE273" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF271" t="inlineStr">
+      <c r="AF273" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG271" t="inlineStr">
+      <c r="AG273" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH271" t="inlineStr">
+      <c r="AH273" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI271" t="inlineStr">
+      <c r="AI273" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ271" t="inlineStr">
+      <c r="AJ273" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK271" t="inlineStr">
+      <c r="AK273" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM271" t="inlineStr">
+      <c r="AM273" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN271" t="b">
+      <c r="AN273" t="b">
         <v>1</v>
       </c>
-      <c r="AO271" t="inlineStr">
+      <c r="AO273" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP271" t="inlineStr">
+      <c r="AP273" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ271" t="inlineStr">
+      <c r="AQ273" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR271" t="inlineStr">
+      <c r="AR273" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS271" t="inlineStr">
+      <c r="AS273" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="AT271" t="n">
+      <c r="AT273" t="n">
         <v>2</v>
       </c>
-      <c r="AU271" t="inlineStr">
+      <c r="AU273" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV271" t="inlineStr">
+      <c r="AV273" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW271" t="inlineStr">
+      <c r="AW273" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX271" t="inlineStr">
+      <c r="AX273" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY271" t="inlineStr">
+      <c r="AY273" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ271" t="inlineStr">
+      <c r="AZ273" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA271" t="inlineStr">
+      <c r="BA273" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB271" t="inlineStr">
+      <c r="BB273" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC271" t="inlineStr">
+      <c r="BC273" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47740,7 +48143,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
@@ -47750,7 +48153,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -47770,7 +48173,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -47802,7 +48205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5778</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -37251,13 +37251,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O211" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R211" t="n">
-        <v>0.1802312029126603</v>
+        <v>0.1782932329888682</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -43021,13 +43021,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O245" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R245" t="n">
-        <v>0.1162781954275228</v>
+        <v>0.1143402255037307</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -46959,12 +46959,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -46989,22 +46989,22 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="O268" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>0.04819169604638021</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -47037,42 +47037,42 @@
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47104,12 +47104,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47156,87 +47156,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47263,7 +47244,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -47312,98 +47293,23 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U270" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN270" t="b">
-        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
@@ -47502,17 +47408,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47546,81 +47452,175 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
-        <v>8</v>
-      </c>
-      <c r="R271" t="n">
-        <v>0.01550375939033637</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
+        <v>1</v>
       </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR271" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47652,12 +47652,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47691,100 +47691,81 @@
         </is>
       </c>
       <c r="N272" t="n">
+        <v>19</v>
+      </c>
+      <c r="O272" t="n">
+        <v>19</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.03682142855204888</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr"/>
+      <c r="AT272" t="n">
         <v>0</v>
       </c>
-      <c r="O272" t="n">
-        <v>0</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0</v>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO272" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP272" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ272" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT272" t="n">
-        <v>2</v>
-      </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47811,7 +47792,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -47860,98 +47841,23 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U273" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG273" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN273" t="b">
-        <v>1</v>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
@@ -48022,6 +47928,245 @@
         </is>
       </c>
       <c r="BC273" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>Legionellose</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN274" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -48143,7 +48288,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -48153,7 +48298,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
@@ -48205,7 +48350,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5810</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -35706,13 +35706,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O201" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R201" t="n">
-        <v>0.1726221555174302</v>
+        <v>0.1689493436979103</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -37251,13 +37251,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O211" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R211" t="n">
-        <v>0.1782932329888682</v>
+        <v>0.1763552630650762</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -41621,13 +41621,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="O236" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="R236" t="n">
-        <v>0.157930908239351</v>
+        <v>0.1762949673369499</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -43021,13 +43021,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O245" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R245" t="n">
-        <v>0.1143402255037307</v>
+        <v>0.1124022555799387</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -47691,13 +47691,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O272" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R272" t="n">
-        <v>0.03682142855204888</v>
+        <v>0.0465112781710091</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -47836,13 +47836,13 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U274" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5878</v>
+        <v>5886</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -41621,13 +41621,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O236" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="R236" t="n">
-        <v>0.1762949673369499</v>
+        <v>0.1909862146150291</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -47104,12 +47104,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47134,12 +47134,12 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N269" t="n">
@@ -47148,6 +47148,9 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -47156,68 +47159,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47244,17 +47256,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47279,12 +47291,12 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N270" t="n">
@@ -47293,23 +47305,101 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="R270" t="n">
+      <c r="P270" t="n">
         <v>0</v>
       </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_180</t>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
@@ -47318,22 +47408,17 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ270" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_180</t>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT270" t="n">
@@ -47341,47 +47426,47 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47408,17 +47493,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47457,170 +47542,76 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD271" t="inlineStr">
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
+      <c r="AT271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE271" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG271" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH271" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI271" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ271" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK271" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
-        </is>
-      </c>
-      <c r="AM271" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN271" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO271" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP271" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AT271" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU271" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV271" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47652,12 +47643,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47691,81 +47682,100 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>0.0465112781710091</v>
+        <v>0</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR272" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47792,17 +47802,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -47836,29 +47846,104 @@
         </is>
       </c>
       <c r="N273" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
         <v>1</v>
       </c>
-      <c r="O273" t="n">
-        <v>1</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47871,7 +47956,7 @@
       </c>
       <c r="AQ273" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR273" t="inlineStr">
@@ -47881,7 +47966,7 @@
       </c>
       <c r="AS273" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT273" t="n">
@@ -47889,47 +47974,47 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47956,219 +48041,673 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>24</v>
+      </c>
+      <c r="O274" t="n">
+        <v>24</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0.0465112781710091</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr"/>
+      <c r="AT274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>1</v>
+      </c>
+      <c r="O275" t="n">
+        <v>1</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
+      <c r="F276" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
+      <c r="G276" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>D107</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
         <is>
           <t>军团菌病</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="K276" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
+      <c r="L276" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr">
+      <c r="M276" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N274" t="n">
+      <c r="N276" t="n">
         <v>1</v>
       </c>
-      <c r="O274" t="n">
+      <c r="O276" t="n">
         <v>1</v>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="U276" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="V274" t="inlineStr">
+      <c r="V276" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="W274" t="inlineStr">
+      <c r="W276" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X274" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>Legionellose</t>
         </is>
       </c>
-      <c r="Y274" t="inlineStr">
+      <c r="Y276" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z274" t="inlineStr">
+      <c r="Z276" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA274" t="inlineStr">
+      <c r="AA276" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB274" t="inlineStr">
+      <c r="AB276" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC274" t="inlineStr">
+      <c r="AC276" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD274" t="inlineStr">
+      <c r="AD276" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE274" t="inlineStr">
+      <c r="AE276" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF274" t="inlineStr">
+      <c r="AF276" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG274" t="inlineStr">
+      <c r="AG276" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH274" t="inlineStr">
+      <c r="AH276" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI274" t="inlineStr">
+      <c r="AI276" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ274" t="inlineStr">
+      <c r="AJ276" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK274" t="inlineStr">
+      <c r="AK276" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM274" t="inlineStr">
+      <c r="AM276" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN274" t="b">
+      <c r="AN276" t="b">
         <v>1</v>
       </c>
-      <c r="AO274" t="inlineStr">
+      <c r="AO276" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP274" t="inlineStr">
+      <c r="AP276" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ274" t="inlineStr">
+      <c r="AQ276" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR274" t="inlineStr">
+      <c r="AR276" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS274" t="inlineStr">
+      <c r="AS276" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="AT274" t="n">
+      <c r="AT276" t="n">
         <v>2</v>
       </c>
-      <c r="AU274" t="inlineStr">
+      <c r="AU276" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV274" t="inlineStr">
+      <c r="AV276" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW274" t="inlineStr">
+      <c r="AW276" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX274" t="inlineStr">
+      <c r="AX276" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY274" t="inlineStr">
+      <c r="AY276" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ274" t="inlineStr">
+      <c r="AZ276" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA274" t="inlineStr">
+      <c r="BA276" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB274" t="inlineStr">
+      <c r="BB276" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC274" t="inlineStr">
+      <c r="BC276" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>137</v>
+      </c>
+      <c r="O277" t="n">
+        <v>137</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0.03925102241894058</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr"/>
+      <c r="AT277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48205,7 +48744,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -48288,7 +48827,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -48298,7 +48837,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
@@ -48318,7 +48857,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -48350,7 +48889,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5886</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -35706,13 +35706,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O201" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R201" t="n">
-        <v>0.1689493436979103</v>
+        <v>0.1726221555174302</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -42011,13 +42011,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O238" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R238" t="n">
-        <v>0.1909862146150291</v>
+        <v>0.1983318382540687</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -43411,13 +43411,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O247" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R247" t="n">
-        <v>0.1124022555799387</v>
+        <v>0.1085263157323546</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O276" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R276" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.05038721801859319</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6077</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -42011,13 +42011,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O238" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R238" t="n">
-        <v>0.1983318382540687</v>
+        <v>0.2020046500735885</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6080</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -42011,13 +42011,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O238" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="R238" t="n">
-        <v>0.2020046500735885</v>
+        <v>0.1946590264345489</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -48072,13 +48072,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R274" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -48236,10 +48236,10 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
@@ -49098,6 +49098,151 @@
       <c r="BC279" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>53</v>
+      </c>
+      <c r="O280" t="n">
+        <v>53</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0.04329084560098561</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
+      <c r="AT280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49134,7 +49279,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -49217,7 +49362,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -49227,7 +49372,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11">
@@ -49279,7 +49424,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6081</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -38189,13 +38189,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O216" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R216" t="n">
-        <v>0.1891260466471829</v>
+        <v>0.1513008373177463</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -38348,10 +38348,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O217" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
@@ -43920,12 +43920,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43959,13 +43959,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="O250" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="R250" t="n">
-        <v>0.2616566519919337</v>
+        <v>0.132388232653028</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -43989,7 +43989,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -43997,62 +43997,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44084,12 +44079,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44123,29 +44118,29 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="O251" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
         <is>
-          <t>Legionellainfektion</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="Y251" t="inlineStr">
@@ -44155,7 +44150,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -44170,7 +44165,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -44205,17 +44200,17 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly legionellosis notifications.</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -44228,7 +44223,7 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
@@ -44236,62 +44231,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44323,12 +44313,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44362,81 +44352,100 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="O252" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="R252" t="n">
-        <v>0.07822246403586412</v>
+        <v>0.2616566519919337</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44463,17 +44472,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44507,81 +44516,175 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="O253" t="n">
-        <v>71</v>
-      </c>
-      <c r="R253" t="n">
-        <v>0.02034177074266263</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>Legionellainfektion</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
+        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44613,12 +44716,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44643,7 +44746,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -44652,13 +44755,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="O254" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="R254" t="n">
-        <v>0.04329084560098561</v>
+        <v>0.07822246403586412</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -44691,42 +44794,42 @@
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -44758,12 +44861,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44788,7 +44891,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -44797,93 +44900,81 @@
         </is>
       </c>
       <c r="N255" t="n">
+        <v>71</v>
+      </c>
+      <c r="O255" t="n">
+        <v>71</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0.02034177074266263</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
+      <c r="AT255" t="n">
         <v>0</v>
       </c>
-      <c r="O255" t="n">
-        <v>0</v>
-      </c>
-      <c r="P255" t="n">
-        <v>0</v>
-      </c>
-      <c r="R255" t="n">
-        <v>0</v>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO255" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP255" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT255" t="n">
-        <v>2</v>
-      </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44910,17 +45001,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -44954,173 +45045,81 @@
         </is>
       </c>
       <c r="N256" t="n">
+        <v>53</v>
+      </c>
+      <c r="O256" t="n">
+        <v>53</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0.04329084560098561</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
+      <c r="AT256" t="n">
         <v>0</v>
       </c>
-      <c r="O256" t="n">
-        <v>0</v>
-      </c>
-      <c r="P256" t="n">
-        <v>0</v>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W256" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y256" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD256" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE256" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF256" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG256" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ256" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK256" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM256" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN256" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO256" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP256" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT256" t="n">
-        <v>2</v>
-      </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45152,12 +45151,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45182,7 +45181,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -45191,81 +45190,93 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
-        <v>92</v>
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>0.02635835082147835</v>
+        <v>0</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45292,17 +45303,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45327,7 +45338,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45336,81 +45347,173 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
-        <v>60</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0.04900850445394597</v>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45442,12 +45545,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45472,7 +45575,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -45481,93 +45584,81 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="O259" t="n">
-        <v>1</v>
-      </c>
-      <c r="P259" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="R259" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.02635835082147835</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45594,17 +45685,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45638,173 +45729,81 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="O260" t="n">
-        <v>1</v>
-      </c>
-      <c r="P260" t="n">
-        <v>1</v>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN260" t="b">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0.04900850445394597</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ260" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45836,12 +45835,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45866,7 +45865,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -45875,81 +45874,93 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>134</v>
+        <v>1</v>
+      </c>
+      <c r="P261" t="n">
+        <v>1</v>
       </c>
       <c r="R261" t="n">
-        <v>0.03839151097910976</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45976,17 +45987,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46011,7 +46022,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -46020,81 +46031,173 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="O262" t="n">
-        <v>45</v>
-      </c>
-      <c r="R262" t="n">
-        <v>0.03675637834045948</v>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P262" t="n">
+        <v>1</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN262" t="b">
+        <v>1</v>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46126,12 +46229,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46156,7 +46259,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -46165,93 +46268,81 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="O263" t="n">
-        <v>2</v>
-      </c>
-      <c r="P263" t="n">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="R263" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.03839151097910976</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ263" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46278,17 +46369,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46322,173 +46413,81 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O264" t="n">
-        <v>2</v>
-      </c>
-      <c r="P264" t="n">
-        <v>2</v>
-      </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W264" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA264" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG264" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK264" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN264" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0.03675637834045948</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46520,12 +46519,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46550,7 +46549,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -46559,81 +46558,93 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="O265" t="n">
-        <v>83</v>
+        <v>2</v>
+      </c>
+      <c r="P265" t="n">
+        <v>2</v>
       </c>
       <c r="R265" t="n">
-        <v>0.0237798165019859</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46660,17 +46671,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46695,7 +46706,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -46704,81 +46715,173 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="O266" t="n">
-        <v>41</v>
-      </c>
-      <c r="R266" t="n">
-        <v>0.03348914471019642</v>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P266" t="n">
+        <v>2</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN266" t="b">
+        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46810,12 +46913,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46840,7 +46943,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -46849,93 +46952,81 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="O267" t="n">
-        <v>2</v>
-      </c>
-      <c r="P267" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="R267" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0237798165019859</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46962,17 +47053,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47006,173 +47097,81 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="O268" t="n">
-        <v>2</v>
-      </c>
-      <c r="P268" t="n">
-        <v>2</v>
-      </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN268" t="b">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0.03348914471019642</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47204,12 +47203,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47234,7 +47233,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -47243,81 +47242,93 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="O269" t="n">
-        <v>116</v>
+        <v>2</v>
+      </c>
+      <c r="P269" t="n">
+        <v>2</v>
       </c>
       <c r="R269" t="n">
-        <v>0.03323444234012487</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47344,17 +47355,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47379,7 +47390,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -47388,81 +47399,173 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="O270" t="n">
-        <v>59</v>
-      </c>
-      <c r="R270" t="n">
-        <v>0.04819169604638021</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P270" t="n">
+        <v>2</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47494,12 +47597,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47524,7 +47627,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -47533,93 +47636,81 @@
         </is>
       </c>
       <c r="N271" t="n">
+        <v>116</v>
+      </c>
+      <c r="O271" t="n">
+        <v>116</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0.03323444234012487</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
+      <c r="AT271" t="n">
         <v>0</v>
       </c>
-      <c r="O271" t="n">
-        <v>0</v>
-      </c>
-      <c r="P271" t="n">
-        <v>0</v>
-      </c>
-      <c r="R271" t="n">
-        <v>0</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO271" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP271" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT271" t="n">
-        <v>2</v>
-      </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47646,17 +47737,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47690,173 +47781,81 @@
         </is>
       </c>
       <c r="N272" t="n">
+        <v>59</v>
+      </c>
+      <c r="O272" t="n">
+        <v>59</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.04819169604638021</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr"/>
+      <c r="AT272" t="n">
         <v>0</v>
       </c>
-      <c r="O272" t="n">
-        <v>0</v>
-      </c>
-      <c r="P272" t="n">
-        <v>0</v>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO272" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP272" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ272" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT272" t="n">
-        <v>2</v>
-      </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47888,12 +47887,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -47918,12 +47917,12 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N273" t="n">
@@ -47932,6 +47931,9 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -47940,68 +47942,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48028,17 +48039,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -48063,37 +48074,115 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
-        <v>2</v>
-      </c>
-      <c r="R274" t="n">
-        <v>0.03557618341728275</v>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P274" t="n">
+        <v>0</v>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_180</t>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN274" t="b">
+        <v>1</v>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
@@ -48102,22 +48191,17 @@
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ274" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR274" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS274" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_180</t>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
         </is>
       </c>
       <c r="AT274" t="n">
@@ -48125,47 +48209,47 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48192,17 +48276,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48236,175 +48320,81 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
-        <v>2</v>
-      </c>
-      <c r="U275" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="W275" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X275" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y275" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA275" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD275" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr"/>
+      <c r="AT275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE275" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF275" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG275" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ275" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK275" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
-        </is>
-      </c>
-      <c r="AM275" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN275" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO275" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP275" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ275" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR275" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AT275" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU275" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV275" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48436,12 +48426,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -48475,81 +48465,100 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="O276" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="R276" t="n">
-        <v>0.05038721801859319</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR276" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS276" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48576,17 +48585,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48620,29 +48629,104 @@
         </is>
       </c>
       <c r="N277" t="n">
+        <v>2</v>
+      </c>
+      <c r="O277" t="n">
+        <v>2</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
         <v>1</v>
       </c>
-      <c r="O277" t="n">
-        <v>1</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -48655,7 +48739,7 @@
       </c>
       <c r="AQ277" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR277" t="inlineStr">
@@ -48665,7 +48749,7 @@
       </c>
       <c r="AS277" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
+          <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
       <c r="AT277" t="n">
@@ -48673,47 +48757,47 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48740,17 +48824,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -48784,175 +48868,81 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="O278" t="n">
-        <v>1</v>
-      </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V278" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W278" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X278" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y278" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA278" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC278" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD278" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE278" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF278" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG278" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ278" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK278" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM278" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN278" t="b">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0.05426315786617728</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48984,12 +48974,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -49014,7 +49004,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -49023,81 +49013,100 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="O279" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="R279" t="n">
-        <v>0.03925102241894058</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR279" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -49124,123 +49133,507 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>1</v>
+      </c>
+      <c r="O280" t="n">
+        <v>1</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>Legionellose</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN280" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>137</v>
+      </c>
+      <c r="O281" t="n">
+        <v>137</v>
+      </c>
+      <c r="R281" t="n">
+        <v>0.03925102241894058</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr"/>
+      <c r="AT281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
+      <c r="G282" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>D107</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
         <is>
           <t>军团菌病</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="K282" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
+      <c r="L282" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr">
+      <c r="M282" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N280" t="n">
+      <c r="N282" t="n">
         <v>53</v>
       </c>
-      <c r="O280" t="n">
+      <c r="O282" t="n">
         <v>53</v>
       </c>
-      <c r="R280" t="n">
+      <c r="R282" t="n">
         <v>0.04329084560098561</v>
       </c>
-      <c r="S280" t="inlineStr">
+      <c r="S282" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO280" t="inlineStr">
+      <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP280" t="inlineStr">
+      <c r="AP282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR280" t="inlineStr">
+      <c r="AR282" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS280" t="inlineStr"/>
-      <c r="AT280" t="n">
+      <c r="AS282" t="inlineStr"/>
+      <c r="AT282" t="n">
         <v>0</v>
       </c>
-      <c r="AU280" t="inlineStr">
+      <c r="AU282" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV280" t="inlineStr">
+      <c r="AV282" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW280" t="inlineStr">
+      <c r="AW282" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX280" t="inlineStr">
+      <c r="AX282" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY280" t="inlineStr">
+      <c r="AY282" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ280" t="inlineStr">
+      <c r="AZ282" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA280" t="inlineStr">
+      <c r="BA282" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB280" t="inlineStr">
+      <c r="BB282" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC280" t="inlineStr">
+      <c r="BC282" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -49362,7 +49755,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -49372,7 +49765,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
@@ -49392,7 +49785,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -49424,7 +49817,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6134</v>
+        <v>6141</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -49013,13 +49013,13 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R279" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -49177,10 +49177,10 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U280" t="inlineStr">
         <is>
@@ -49817,7 +49817,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6141</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -35706,13 +35706,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O201" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R201" t="n">
-        <v>0.1726221555174302</v>
+        <v>0.1762949673369499</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -42011,13 +42011,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="O238" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="R238" t="n">
-        <v>0.1946590264345489</v>
+        <v>0.1652765318783906</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -43411,13 +43411,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O247" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="R247" t="n">
-        <v>0.1085263157323546</v>
+        <v>0.1124022555799387</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -48868,13 +48868,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="O278" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="R278" t="n">
-        <v>0.05426315786617728</v>
+        <v>0.09496052626581025</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -49636,6 +49636,545 @@
       <c r="BC282" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>1</v>
+      </c>
+      <c r="O283" t="n">
+        <v>1</v>
+      </c>
+      <c r="P283" t="n">
+        <v>1</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>1</v>
+      </c>
+      <c r="O284" t="n">
+        <v>1</v>
+      </c>
+      <c r="P284" t="n">
+        <v>1</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ284" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM284" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN284" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>99</v>
+      </c>
+      <c r="O285" t="n">
+        <v>99</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0.02836387751441691</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr"/>
+      <c r="AT285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -49672,7 +50211,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -49755,7 +50294,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -49765,7 +50304,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11">
@@ -49785,7 +50324,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -49817,7 +50356,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6143</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -48868,13 +48868,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="O278" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="R278" t="n">
-        <v>0.09496052626581025</v>
+        <v>0.1065883458085625</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6259</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -42011,13 +42011,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O238" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R238" t="n">
-        <v>0.1652765318783906</v>
+        <v>0.1689493436979103</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -43372,12 +43372,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -43411,13 +43411,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="O247" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="R247" t="n">
-        <v>0.1124022555799387</v>
+        <v>0.4201337868609799</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -43450,42 +43450,42 @@
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43517,12 +43517,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43556,100 +43556,81 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="O248" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="R248" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1143402255037307</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43676,7 +43657,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -43725,98 +43706,23 @@
       <c r="O249" t="n">
         <v>5</v>
       </c>
+      <c r="R249" t="n">
+        <v>0.08844879128977531</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U249" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM249" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN249" t="b">
-        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
@@ -43915,17 +43821,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43959,22 +43865,39 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O250" t="n">
-        <v>7</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.132388232653028</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Legionellose</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -43982,6 +43905,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43989,7 +43970,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -43997,57 +43978,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44074,7 +44060,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -44123,98 +44109,23 @@
       <c r="O251" t="n">
         <v>7</v>
       </c>
+      <c r="R251" t="n">
+        <v>0.132388232653028</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U251" t="inlineStr">
         <is>
           <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly legionellosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
@@ -44308,17 +44219,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44352,22 +44263,39 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="O252" t="n">
-        <v>28</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.2616566519919337</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -44375,6 +44303,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly legionellosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44382,7 +44368,7 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
@@ -44390,62 +44376,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+          <t>SER_NZ_LEGIONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44472,7 +44453,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -44516,103 +44497,28 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O253" t="n">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0.2523117715636503</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
         </is>
       </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Legionellainfektion</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
@@ -44711,17 +44617,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44755,81 +44661,175 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="O254" t="n">
-        <v>18</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.07822246403586412</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Legionellainfektion</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR254" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44861,12 +44861,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44900,13 +44900,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="O255" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="R255" t="n">
-        <v>0.02034177074266263</v>
+        <v>0.07822246403586412</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -44939,42 +44939,42 @@
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -45006,12 +45006,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45036,7 +45036,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -45045,13 +45045,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="O256" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="R256" t="n">
-        <v>0.04329084560098561</v>
+        <v>0.02034177074266263</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -45084,42 +45084,42 @@
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45151,12 +45151,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45190,93 +45190,81 @@
         </is>
       </c>
       <c r="N257" t="n">
+        <v>53</v>
+      </c>
+      <c r="O257" t="n">
+        <v>53</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0.04329084560098561</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
+      <c r="AT257" t="n">
         <v>0</v>
       </c>
-      <c r="O257" t="n">
-        <v>0</v>
-      </c>
-      <c r="P257" t="n">
-        <v>0</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP257" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT257" t="n">
-        <v>2</v>
-      </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45303,7 +45291,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -45355,98 +45343,18 @@
       <c r="P258" t="n">
         <v>0</v>
       </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN258" t="b">
-        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
@@ -45540,17 +45448,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45575,7 +45483,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -45584,81 +45492,173 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
-        <v>92</v>
-      </c>
-      <c r="R259" t="n">
-        <v>0.02635835082147835</v>
-      </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN259" t="b">
+        <v>1</v>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45690,12 +45690,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45720,7 +45720,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -45729,13 +45729,13 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="O260" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="R260" t="n">
-        <v>0.04900850445394597</v>
+        <v>0.02635835082147835</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -45768,42 +45768,42 @@
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45835,12 +45835,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45874,93 +45874,81 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="O261" t="n">
-        <v>1</v>
-      </c>
-      <c r="P261" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="R261" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.04900850445394597</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA261" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ261" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45987,7 +45975,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -46039,98 +46027,18 @@
       <c r="P262" t="n">
         <v>1</v>
       </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R262" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE262" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG262" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM262" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN262" t="b">
-        <v>1</v>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
@@ -46224,17 +46132,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46259,7 +46167,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -46268,81 +46176,173 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="O263" t="n">
-        <v>134</v>
-      </c>
-      <c r="R263" t="n">
-        <v>0.03839151097910976</v>
-      </c>
-      <c r="S263" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P263" t="n">
+        <v>1</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN263" t="b">
+        <v>1</v>
       </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46374,12 +46374,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46404,7 +46404,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -46413,13 +46413,13 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="O264" t="n">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="R264" t="n">
-        <v>0.03675637834045948</v>
+        <v>0.03839151097910976</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -46452,42 +46452,42 @@
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46519,12 +46519,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46558,93 +46558,81 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O265" t="n">
-        <v>2</v>
-      </c>
-      <c r="P265" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="R265" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.03675637834045948</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46671,7 +46659,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -46723,98 +46711,18 @@
       <c r="P266" t="n">
         <v>2</v>
       </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R266" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ266" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK266" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM266" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN266" t="b">
-        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
@@ -46908,17 +46816,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46943,7 +46851,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -46952,81 +46860,173 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="O267" t="n">
-        <v>83</v>
-      </c>
-      <c r="R267" t="n">
-        <v>0.0237798165019859</v>
-      </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P267" t="n">
+        <v>2</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN267" t="b">
+        <v>1</v>
       </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47088,7 +47088,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -47097,13 +47097,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="O268" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="R268" t="n">
-        <v>0.03348914471019642</v>
+        <v>0.0237798165019859</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -47136,42 +47136,42 @@
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47203,12 +47203,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47242,93 +47242,81 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="O269" t="n">
-        <v>2</v>
-      </c>
-      <c r="P269" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="R269" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.03348914471019642</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47355,7 +47343,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -47407,98 +47395,18 @@
       <c r="P270" t="n">
         <v>2</v>
       </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R270" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN270" t="b">
-        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
@@ -47592,17 +47500,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47627,7 +47535,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -47636,81 +47544,173 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="O271" t="n">
-        <v>116</v>
-      </c>
-      <c r="R271" t="n">
-        <v>0.03323444234012487</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P271" t="n">
+        <v>2</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
+        <v>1</v>
       </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47742,12 +47742,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47772,7 +47772,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -47781,13 +47781,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="O272" t="n">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="R272" t="n">
-        <v>0.04819169604638021</v>
+        <v>0.03323444234012487</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -47820,42 +47820,42 @@
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47887,12 +47887,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -47926,93 +47926,81 @@
         </is>
       </c>
       <c r="N273" t="n">
+        <v>59</v>
+      </c>
+      <c r="O273" t="n">
+        <v>59</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0.04819169604638021</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr"/>
+      <c r="AT273" t="n">
         <v>0</v>
       </c>
-      <c r="O273" t="n">
-        <v>0</v>
-      </c>
-      <c r="P273" t="n">
-        <v>0</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO273" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP273" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ273" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="AT273" t="n">
-        <v>2</v>
-      </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48039,7 +48027,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -48091,98 +48079,18 @@
       <c r="P274" t="n">
         <v>0</v>
       </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R274" t="n">
+        <v>0</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN274" t="b">
-        <v>1</v>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
@@ -48276,17 +48184,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48311,12 +48219,12 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N275" t="n">
@@ -48325,76 +48233,168 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="R275" t="n">
+      <c r="P275" t="n">
         <v>0</v>
       </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN275" t="b">
+        <v>1</v>
       </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR275" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
       <c r="AT275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48426,12 +48426,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -48465,100 +48465,81 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>0.03557618341728275</v>
+        <v>0</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="AA276" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ276" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR276" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS276" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr"/>
       <c r="AT276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48585,7 +48566,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -48629,103 +48610,28 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O277" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U277" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_180</t>
         </is>
       </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_180</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA277" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ277" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN277" t="b">
-        <v>1</v>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
@@ -48824,17 +48730,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -48868,81 +48774,175 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="O278" t="n">
-        <v>55</v>
-      </c>
-      <c r="R278" t="n">
-        <v>0.1065883458085625</v>
-      </c>
-      <c r="S278" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ278" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM278" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN278" t="b">
+        <v>1</v>
       </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48974,12 +48974,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -49013,100 +49013,81 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="O279" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="R279" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.1317819548178591</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA279" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ279" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR279" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr"/>
       <c r="AT279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -49133,7 +49114,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -49177,103 +49158,28 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O280" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U280" t="inlineStr">
         <is>
           <t>SER_NO_FHI_602_MONTHLY</t>
         </is>
       </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_602_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X280" t="inlineStr">
-        <is>
-          <t>Legionellose</t>
-        </is>
-      </c>
-      <c r="Y280" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD280" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE280" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF280" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG280" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI280" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ280" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK280" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM280" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN280" t="b">
-        <v>1</v>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
@@ -49372,17 +49278,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -49407,7 +49313,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -49416,81 +49322,175 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="O281" t="n">
-        <v>137</v>
-      </c>
-      <c r="R281" t="n">
-        <v>0.03925102241894058</v>
-      </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>Legionellose</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN281" t="b">
+        <v>1</v>
       </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR281" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS281" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_602_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -49522,12 +49522,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -49552,7 +49552,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -49561,13 +49561,13 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="O282" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="R282" t="n">
-        <v>0.04329084560098561</v>
+        <v>0.03925102241894058</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -49600,42 +49600,42 @@
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -49667,12 +49667,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -49706,93 +49706,81 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="O283" t="n">
-        <v>1</v>
-      </c>
-      <c r="P283" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="R283" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.04329084560098561</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA283" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO283" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ283" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS283" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr"/>
       <c r="AT283" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49819,7 +49807,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -49871,98 +49859,18 @@
       <c r="P284" t="n">
         <v>1</v>
       </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_LEGIONELLOSIS</t>
-        </is>
-      </c>
-      <c r="W284" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X284" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="Y284" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R284" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC284" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD284" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE284" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF284" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG284" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH284" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI284" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ284" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK284" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM284" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN284" t="b">
-        <v>1</v>
       </c>
       <c r="AO284" t="inlineStr">
         <is>
@@ -50056,123 +49964,1044 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>1</v>
+      </c>
+      <c r="O285" t="n">
+        <v>1</v>
+      </c>
+      <c r="P285" t="n">
+        <v>1</v>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ285" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK285" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM285" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN285" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
+      <c r="F286" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
+      <c r="G286" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>D107</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>Legionellosis</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr">
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
         <is>
           <t>军团菌病</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="K286" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
+      <c r="L286" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M285" t="inlineStr">
+      <c r="M286" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N285" t="n">
+      <c r="N286" t="n">
         <v>99</v>
       </c>
-      <c r="O285" t="n">
+      <c r="O286" t="n">
         <v>99</v>
       </c>
-      <c r="R285" t="n">
+      <c r="R286" t="n">
         <v>0.02836387751441691</v>
       </c>
-      <c r="S285" t="inlineStr">
+      <c r="S286" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO285" t="inlineStr">
+      <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP285" t="inlineStr">
+      <c r="AP286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR285" t="inlineStr">
+      <c r="AR286" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS285" t="inlineStr"/>
-      <c r="AT285" t="n">
+      <c r="AS286" t="inlineStr"/>
+      <c r="AT286" t="n">
         <v>0</v>
       </c>
-      <c r="AU285" t="inlineStr">
+      <c r="AU286" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV285" t="inlineStr">
+      <c r="AV286" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW285" t="inlineStr">
+      <c r="AW286" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX285" t="inlineStr">
+      <c r="AX286" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY285" t="inlineStr">
+      <c r="AY286" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ285" t="inlineStr">
+      <c r="AZ286" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA285" t="inlineStr">
+      <c r="BA286" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB285" t="inlineStr">
+      <c r="BB286" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC285" t="inlineStr">
+      <c r="BC286" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>57</v>
+      </c>
+      <c r="O287" t="n">
+        <v>57</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0.04655807923124868</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR287" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr"/>
+      <c r="AT287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>3</v>
+      </c>
+      <c r="O288" t="n">
+        <v>3</v>
+      </c>
+      <c r="P288" t="n">
+        <v>3</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>3</v>
+      </c>
+      <c r="O289" t="n">
+        <v>3</v>
+      </c>
+      <c r="P289" t="n">
+        <v>3</v>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD289" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ289" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK289" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM289" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN289" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ289" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>123</v>
+      </c>
+      <c r="O290" t="n">
+        <v>123</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0.03523996903306344</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr"/>
+      <c r="AT290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -50211,7 +51040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -50294,7 +51123,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -50304,7 +51133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11">
@@ -50324,7 +51153,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -50356,7 +51185,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6265</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -35706,13 +35706,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O201" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R201" t="n">
-        <v>0.1762949673369499</v>
+        <v>0.1726221555174302</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -37641,13 +37641,13 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O213" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R213" t="n">
-        <v>0.1763552630650762</v>
+        <v>0.1744172931412841</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -48465,13 +48465,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>0.1726221555174302</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -49013,13 +49013,13 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="O279" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="R279" t="n">
-        <v>0.1317819548178591</v>
+        <v>0.1627894735985319</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -51004,6 +51004,1238 @@
       <c r="BC290" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>86</v>
+      </c>
+      <c r="O291" t="n">
+        <v>86</v>
+      </c>
+      <c r="R291" t="n">
+        <v>0.0702455230506559</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr"/>
+      <c r="AT291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>2</v>
+      </c>
+      <c r="O292" t="n">
+        <v>2</v>
+      </c>
+      <c r="P292" t="n">
+        <v>2</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV292" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA292" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB292" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC292" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>2</v>
+      </c>
+      <c r="O293" t="n">
+        <v>2</v>
+      </c>
+      <c r="P293" t="n">
+        <v>2</v>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD293" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH293" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI293" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ293" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK293" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM293" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN293" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ293" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_LEGIONELLOSIS; SER_SG_HIST_LEGIONELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>135</v>
+      </c>
+      <c r="O294" t="n">
+        <v>135</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0.0386780147923867</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr"/>
+      <c r="AT294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV294" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA294" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB294" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC294" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ295" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AT295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU295" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV295" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA295" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB295" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC295" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC296" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD296" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF296" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH296" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI296" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ296" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK296" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 180.</t>
+        </is>
+      </c>
+      <c r="AM296" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN296" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP296" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ296" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS296" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_180</t>
+        </is>
+      </c>
+      <c r="AT296" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV296" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA296" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB296" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC296" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>1</v>
+      </c>
+      <c r="O297" t="n">
+        <v>1</v>
+      </c>
+      <c r="R297" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO297" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP297" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR297" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS297" t="inlineStr"/>
+      <c r="AT297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU297" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV297" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA297" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB297" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC297" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -51040,7 +52272,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -51123,7 +52355,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10">
@@ -51133,7 +52365,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11">
@@ -51153,7 +52385,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -51185,7 +52417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6500</v>
+        <v>6785</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -48465,13 +48465,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O276" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R276" t="n">
-        <v>0.1726221555174302</v>
+        <v>0.1652765318783906</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6785</v>
+        <v>6783</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -31882,7 +31882,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -38042,7 +38042,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43957,7 +43957,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -49158,13 +49158,13 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O280" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R280" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -49322,10 +49322,10 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O281" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U281" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -52417,7 +52417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6783</v>
+        <v>6785</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -56717,13 +56717,13 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O333" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="R333" t="n">
-        <v>0.1666654134461159</v>
+        <v>0.1724793232174921</v>
       </c>
       <c r="S333" t="inlineStr">
         <is>
@@ -60010,13 +60010,13 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O352" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R352" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -60266,7 +60266,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7239</v>
+        <v>7244</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -56217,13 +56217,13 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O325" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R325" t="n">
-        <v>0.1799677791564697</v>
+        <v>0.1873134027955093</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
@@ -57549,13 +57549,13 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O334" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R334" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S334" t="inlineStr">
         <is>
@@ -57713,10 +57713,10 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O335" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U335" t="inlineStr">
         <is>
@@ -57952,13 +57952,13 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O336" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R336" t="n">
-        <v>0.1724793232174921</v>
+        <v>0.1763552630650762</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
@@ -62067,13 +62067,13 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O359" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R359" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S359" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7532</v>
+        <v>7539</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -48998,13 +48998,13 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O283" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="R283" t="n">
-        <v>0.2166958973516676</v>
+        <v>0.209350273712628</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
@@ -56217,13 +56217,13 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O325" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R325" t="n">
-        <v>0.1873134027955093</v>
+        <v>0.1946590264345489</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
@@ -62067,13 +62067,13 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O359" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R359" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S359" t="inlineStr">
         <is>
@@ -62217,13 +62217,13 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O360" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R360" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -62381,10 +62381,10 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O361" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U361" t="inlineStr">
         <is>
@@ -62700,6 +62700,151 @@
       <c r="BC362" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N363" t="n">
+        <v>66</v>
+      </c>
+      <c r="O363" t="n">
+        <v>66</v>
+      </c>
+      <c r="R363" t="n">
+        <v>0.05390935489934058</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO363" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP363" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR363" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr"/>
+      <c r="AT363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU363" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV363" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW363" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX363" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY363" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA363" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB363" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC363" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -62736,7 +62881,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -62819,7 +62964,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -62829,7 +62974,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11">
@@ -62881,7 +63026,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7539</v>
+        <v>7619</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d107/2026-2029.xlsx
+++ b/diseases/d107/2026-2029.xlsx
@@ -4702,9 +4702,6 @@
       <c r="O25" t="n">
         <v>8</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.002292030506215508</v>
       </c>
@@ -5397,9 +5394,6 @@
       <c r="O29" t="n">
         <v>53</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01518470210367774</v>
       </c>
@@ -6092,9 +6086,6 @@
       <c r="O33" t="n">
         <v>42</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.01203316015763142</v>
       </c>
@@ -6787,9 +6778,6 @@
       <c r="O37" t="n">
         <v>42</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.01203316015763142</v>
       </c>
@@ -7482,9 +7470,6 @@
       <c r="O41" t="n">
         <v>39</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.0111736487178006</v>
       </c>
@@ -12096,9 +12081,6 @@
       <c r="O68" t="n">
         <v>48</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.01375218303729305</v>
       </c>
@@ -12791,9 +12773,6 @@
       <c r="O72" t="n">
         <v>45</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.01289267159746223</v>
       </c>
@@ -13486,9 +13465,6 @@
       <c r="O76" t="n">
         <v>48</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.01375218303729305</v>
       </c>
@@ -14181,9 +14157,6 @@
       <c r="O80" t="n">
         <v>36</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.01031413727796979</v>
       </c>
@@ -18822,9 +18795,6 @@
       <c r="O107" t="n">
         <v>51</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.01461169447712387</v>
       </c>
@@ -19517,9 +19487,6 @@
       <c r="O111" t="n">
         <v>37</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -20212,9 +20179,6 @@
       <c r="O115" t="n">
         <v>56</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.01604421354350856</v>
       </c>
@@ -20902,16 +20866,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O119" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R119" t="n">
-        <v>0.01432519066384693</v>
+        <v>0.01403868685056999</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -25503,9 +25464,6 @@
       <c r="O146" t="n">
         <v>40</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.01146015253107754</v>
       </c>
@@ -26198,9 +26156,6 @@
       <c r="O150" t="n">
         <v>41</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.01174665634435448</v>
       </c>
@@ -26893,9 +26848,6 @@
       <c r="O154" t="n">
         <v>37</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -27583,16 +27535,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O158" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R158" t="n">
-        <v>0.01231966397090836</v>
+        <v>0.01203316015763142</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -32193,9 +32142,6 @@
       <c r="O185" t="n">
         <v>61</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.01747673260989325</v>
       </c>
@@ -32888,9 +32834,6 @@
       <c r="O189" t="n">
         <v>47</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.01346567922401611</v>
       </c>
@@ -33583,9 +33526,6 @@
       <c r="O193" t="n">
         <v>66</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.01890925167627794</v>
       </c>
@@ -34278,9 +34218,6 @@
       <c r="O197" t="n">
         <v>19</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.005443572452261832</v>
       </c>
@@ -45544,13 +45481,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O263" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R263" t="n">
-        <v>0.2616566519919337</v>
+        <v>0.2523117715636503</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -45708,10 +45645,10 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O264" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U264" t="inlineStr">
         <is>
@@ -62845,6 +62782,156 @@
       <c r="BC363" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>legionellosis</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>104</v>
+      </c>
+      <c r="O364" t="n">
+        <v>104</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0.0297963965808016</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR364" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr"/>
+      <c r="AT364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU364" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV364" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW364" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX364" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY364" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA364" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB364" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC364" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -62881,7 +62968,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -62964,7 +63051,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -62974,7 +63061,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11">
@@ -63026,7 +63113,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7619</v>
+        <v>7720</v>
       </c>
     </row>
     <row r="16">
